--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -674,7 +674,7 @@
         <v>48</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -895,7 +895,7 @@
         <v>48</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>test_success</t>
+  </si>
+  <si>
+    <t>test_success_2</t>
   </si>
   <si>
     <t>test_API_SA_PreFetch_01</t>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -549,10 +552,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -566,10 +569,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -583,10 +586,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -600,10 +603,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -617,10 +620,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -634,10 +637,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -651,10 +654,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -668,10 +671,10 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -685,10 +688,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -702,10 +705,10 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -719,10 +722,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -736,10 +739,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -753,10 +756,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -770,10 +773,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -787,10 +790,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -804,10 +807,10 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -821,10 +824,10 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -838,10 +841,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -855,10 +858,10 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -872,10 +875,10 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -889,10 +892,10 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -900,7 +903,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
@@ -912,7 +915,7 @@
         <v>49</v>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -934,16 +937,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -951,18 +954,35 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -558,7 +558,7 @@
         <v>49</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -898,7 +898,7 @@
         <v>49</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -915,7 +915,7 @@
         <v>49</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,25 +935,25 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>test_API_SA_PreFetch_01</t>
+          <t>test_success_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
+          <t>test_sample</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>API_DB/SA</t>
+          <t>UI/SA</t>
         </is>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -962,17 +962,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>test_GUI_APP_Branding_Ezetap_01</t>
+          <t>test_API_SA_PreFetch_01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GUI/APP/test_GUI_APP_Branding</t>
+          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GUI/APP</t>
+          <t>API_DB/SA</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -981,11 +981,11 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>test_GUI_APP_Branding_Axis_02</t>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1004,24 +1004,47 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Axis_02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GUI/APP/test_GUI_APP_Branding</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GUI/APP</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>test_GUI_APP_Branding_Hdfc_03</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GUI/APP/test_GUI_APP_Branding</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>GUI/APP</t>
         </is>
       </c>
-      <c r="E26" t="b">
+      <c r="E27" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -558,7 +558,7 @@
         <v>49</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -626,7 +626,7 @@
         <v>49</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -660,7 +660,7 @@
         <v>49</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -796,7 +796,7 @@
         <v>49</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,26 +999,26 @@
         </is>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>test_UI_MPOS_PM_UPI_Pending_HDFC_03</t>
+          <t>test_API_SA_PreFetch_01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/home/ezetap/EzeAuto/TestCases/Functional/UI/MPOS/test_UPI_Payment</t>
+          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UI/MPOS</t>
+          <t>API_DB/SA</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1027,44 +1027,44 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>test_UI_MPOS_PM_UPI_Refund_HDFC_04</t>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/home/ezetap/EzeAuto/TestCases/Functional/UI/MPOS/test_UPI_Payment</t>
+          <t>GUI/APP/test_GUI_APP_Branding</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UI/MPOS</t>
+          <t>GUI/APP</t>
         </is>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>test_API_SA_PreFetch_01</t>
+          <t>test_GUI_APP_Branding_Axis_02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
+          <t>GUI/APP/test_GUI_APP_Branding</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>API_DB/SA</t>
+          <t>GUI/APP</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1073,11 +1073,11 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>test_GUI_APP_Branding_Ezetap_01</t>
+          <t>test_GUI_APP_Branding_Hdfc_03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1091,52 +1091,6 @@
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>test_GUI_APP_Branding_Axis_02</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>GUI/APP/test_GUI_APP_Branding</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>GUI/APP</t>
-        </is>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>test_GUI_APP_Branding_Hdfc_03</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>GUI/APP/test_GUI_APP_Branding</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>GUI/APP</t>
-        </is>
-      </c>
-      <c r="E31" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TestCases/AllTestcaseSuite.xlsx
+++ b/TestCases/AllTestcaseSuite.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,26 +999,26 @@
         </is>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>test_API_SA_PreFetch_01</t>
+          <t>test_UI_MPOS_PM_UPI_Pending_HDFC_03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
+          <t>/home/ezetap/EzeAuto/TestCases/Functional/UI/MPOS/test_UPI_Payment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>API_DB/SA</t>
+          <t>UI/MPOS</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1027,44 +1027,44 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>test_GUI_APP_Branding_Ezetap_01</t>
+          <t>test_UI_MPOS_PM_UPI_Refund_HDFC_04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GUI/APP/test_GUI_APP_Branding</t>
+          <t>/home/ezetap/EzeAuto/TestCases/Functional/UI/MPOS/test_UPI_Payment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUI/APP</t>
+          <t>UI/MPOS</t>
         </is>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>test_GUI_APP_Branding_Axis_02</t>
+          <t>test_API_SA_PreFetch_01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GUI/APP/test_GUI_APP_Branding</t>
+          <t>Functional/API_DB/SA/test_API_SA_PreFetch</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUI/APP</t>
+          <t>API_DB/SA</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1073,24 +1073,70 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GUI/APP/test_GUI_APP_Branding</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GUI/APP</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Axis_02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GUI/APP/test_GUI_APP_Branding</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GUI/APP</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>test_GUI_APP_Branding_Hdfc_03</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GUI/APP/test_GUI_APP_Branding</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>GUI/APP</t>
         </is>
       </c>
-      <c r="E29" t="b">
+      <c r="E31" t="b">
         <v>0</v>
       </c>
     </row>
